--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>706</v>
+        <v>735</v>
       </c>
       <c r="C2">
-        <v>1158</v>
+        <v>1194</v>
       </c>
       <c r="D2">
-        <v>1444</v>
+        <v>1465</v>
       </c>
       <c r="E2">
-        <v>1589</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>713</v>
+        <v>766</v>
       </c>
       <c r="C3">
-        <v>1167</v>
+        <v>1215</v>
       </c>
       <c r="D3">
-        <v>1451</v>
+        <v>1473</v>
       </c>
       <c r="E3">
-        <v>1594</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="C4">
-        <v>1103</v>
+        <v>1115</v>
       </c>
       <c r="D4">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="E4">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="C5">
-        <v>1177</v>
+        <v>1238</v>
       </c>
       <c r="D5">
-        <v>1454</v>
+        <v>1482</v>
       </c>
       <c r="E5">
-        <v>1604</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>672</v>
+        <v>733</v>
       </c>
       <c r="C6">
-        <v>1141</v>
+        <v>1193</v>
       </c>
       <c r="D6">
-        <v>1438</v>
+        <v>1464</v>
       </c>
       <c r="E6">
-        <v>1592</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="C7">
-        <v>1208</v>
+        <v>1243</v>
       </c>
       <c r="D7">
-        <v>1483</v>
+        <v>1507</v>
       </c>
       <c r="E7">
-        <v>1606</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>357</v>
+        <v>512</v>
       </c>
       <c r="C8">
-        <v>807</v>
+        <v>967</v>
       </c>
       <c r="D8">
-        <v>1182</v>
+        <v>1313</v>
       </c>
       <c r="E8">
-        <v>1466</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>666</v>
+        <v>807</v>
       </c>
       <c r="C9">
-        <v>1119</v>
+        <v>1230</v>
       </c>
       <c r="D9">
-        <v>1421</v>
+        <v>1466</v>
       </c>
       <c r="E9">
-        <v>1566</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>797</v>
+        <v>840</v>
       </c>
       <c r="C10">
-        <v>1256</v>
+        <v>1286</v>
       </c>
       <c r="D10">
-        <v>1513</v>
+        <v>1526</v>
       </c>
       <c r="E10">
-        <v>1641</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="C11">
-        <v>1249</v>
+        <v>1273</v>
       </c>
       <c r="D11">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="E11">
-        <v>1637</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>721</v>
+        <v>841</v>
       </c>
       <c r="C12">
-        <v>1193</v>
+        <v>1256</v>
       </c>
       <c r="D12">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="E12">
-        <v>1606</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>774</v>
+        <v>817</v>
       </c>
       <c r="C13">
-        <v>1238</v>
+        <v>1263</v>
       </c>
       <c r="D13">
-        <v>1502</v>
+        <v>1513</v>
       </c>
       <c r="E13">
-        <v>1631</v>
+        <v>1639</v>
       </c>
     </row>
   </sheetData>
